--- a/data/trans_orig/IP07KS_C07_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C07_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de trato justo por parte de sus padres en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de trato justo por parte de sus padres, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31726</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26280</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35739</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>79,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>65,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20308</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15168</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24208</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>66,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31503</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35004</t>
+          <t>25307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>52975</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>45323</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57148</t>
+          <t>58892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8153</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4140</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13599</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9006</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5557</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14378</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29,54%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>17794</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23316</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3573</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3088</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2316</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2224</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20907</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15220</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25311</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20454</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15545</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24080</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>70,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41307</t>
+          <t>42238</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>34947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47305</t>
+          <t>48211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10454</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16420</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4453</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13066</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3273</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4892</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5068</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3547</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6162</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6414</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5718</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15656</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10499</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20253</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>38,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8960</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5739</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11783</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>61,58%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>59,2%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>37,23%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>80,41%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>24871</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>19357</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>30279</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>58,47%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>39,19%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>76,43%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>25148</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>18816</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>30369</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>59,54%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10286</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15583</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,77%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>5589</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2766</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>38,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16450</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22550</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6405</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>4821</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>23,14%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>4837</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>44040</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>33603</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>52450</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>63,45%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>48,41%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>75,56%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>31053</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>11006</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>54037</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>46,24%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>80,47%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>31648</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>24135</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>75688</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40988</t>
+          <t>64014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99900</t>
+          <t>85452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>75,6%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20901</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12674</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>32246</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>30,11%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>18,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>46,45%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>36102</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>13118</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>56149</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>53,76%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>83,61%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21206</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34123</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>57308</t>
+          <t>32869</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94755</t>
+          <t>45044</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -2992,107 +2992,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>498</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2487</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>6796</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>476</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3967</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3980</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4055</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4747</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>5095</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>38255</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>30114</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>46899</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>65,34%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>51,44%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>80,1%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>22199</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>17583</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>26670</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>62,17%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>74,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>29132</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>63158</t>
+          <t>62030</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53513</t>
+          <t>52378</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74497</t>
+          <t>73264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13937</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7437</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>21837</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>23,8%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>9742</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>6111</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>14784</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>41,4%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16600</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>58548</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>58548</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>58548</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60184</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60184</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60184</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>95894</t>
+          <t>97524</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>95894</t>
+          <t>97524</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>95894</t>
+          <t>97524</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>19016</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>13561</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>24645</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>52,07%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>37,13%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>67,48%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>16998</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>12399</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>21662</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>56,33%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>71,78%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24280</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>35994</t>
+          <t>37410</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28829</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42782</t>
+          <t>45024</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>15044</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>9505</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>20334</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>26,03%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>55,68%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>11275</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>7171</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>16312</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>23,76%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>35750</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -4582,107 +4582,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>937</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>995</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>5253</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>4039</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>995</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>5780</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>169600</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>154269</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>186983</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>64,11%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>70,69%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>119971</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>73547</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>142065</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>57,89%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>35,49%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>68,55%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>173500</t>
+          <t>125611</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>155368</t>
+          <t>112697</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>191435</t>
+          <t>136468</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>293471</t>
+          <t>295211</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>228391</t>
+          <t>273988</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>320389</t>
+          <t>317016</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>78774</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>64053</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>94481</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>24,21%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>35,72%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>79716</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>56622</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>133054</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>38,46%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>64,2%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>60268</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>49192</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>93587</t>
+          <t>73153</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>156416</t>
+          <t>139042</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>129625</t>
+          <t>120192</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>231172</t>
+          <t>160001</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11247</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>19500</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>2868</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>12112</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>27274</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -5151,107 +5151,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>4281</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>4038</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>3907</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>3722</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>9094</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>3084</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2687</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>3761</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>9173</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>264530</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>264530</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>264530</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266286</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266286</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266286</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>473532</t>
+          <t>458619</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>473532</t>
+          <t>458619</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>473532</t>
+          <t>458619</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
